--- a/terminology/CodeSystem-mkn-10.xlsx
+++ b/terminology/CodeSystem-mkn-10.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>2025-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>1980-01-01</t>
+    <t>2025-12-22T17:42:13.32582Z</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,7 +89,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Národní systém pro kódování diagnóz a zdravotních problémů.</t>
+    <t>Národní systém pro kódování diagnóz a zdravotních problémů odvozený od ICD-10 WHO.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -101,13 +101,13 @@
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Value Set (all codes)</t>
   </si>
   <si>
     <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>is-a</t>
   </si>
   <si>
     <t>Compositional</t>
@@ -387,20 +387,22 @@
         <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
